--- a/Amaan_Internship_Ecosystem_v2.xlsx
+++ b/Amaan_Internship_Ecosystem_v2.xlsx
@@ -6,21 +6,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Career_Profile" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Skills" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Jobs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Applications" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Interviews" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Analytics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="AI_Import" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="AI_Import_Guide" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Morning Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Career_Profile" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Skills" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Jobs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Applications" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Interviews" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Analytics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AI_Import" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="AI_Import_Guide" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jobs'!$A$1:$Z$500</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Applications'!$A$1:$Q$500</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Interviews'!$A$1:$O$500</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AI_Import'!$A$1:$AK$499</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Morning Dashboard'!$A$9:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Jobs'!$A$1:$Z$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Applications'!$A$1:$Q$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Interviews'!$A$1:$O$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'AI_Import'!$A$1:$AK$499</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +63,30 @@
       <color rgb="FFFFFFFF"/>
       <sz val="15"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +96,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,10 +177,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -172,9 +207,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -546,6 +596,443 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>AMAAN INTERNSHIP ECOSYSTEM — MORNING DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Updated: 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Workflow: Discover → Analyze → Shortlist → Apply → Track</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Relevant/Tracked Jobs</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Ready to Review</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>APPLY ASAP</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>544</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Tip:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Click the Role to open the job. Apply manually, then record it in Applications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Work Mode</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>Stipend</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>Application Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>SubSpace</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>APPLY</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>₹30,000–40,001 headline; fixed ₹20,000–30,000 + incentive ₹10,000–10,001</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Nutrithy Wellness</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Software Development Engineering Intern</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>APPLY ASAP</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>₹20,000- ₹30,000 /month</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Amaanuddin_Ahmed_Fullstack_Resume.pdf</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>NOT APPLIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>MORNING ROUTINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1. Start with APPLY ASAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2. Open the job by clicking its Role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3. Apply manually if you want to proceed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4. Add the application to the Applications sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5. Run daily.py tomorrow; the dashboard will move applied jobs out of the action list.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A9:K11"/>
+  <mergeCells count="8">
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A17:K17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="39" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>AI → CRM workflow</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Run a JD through the AI Job Analyzer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Copy the structured JSON result into the importer script/tool we will build next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>The importer maps the analysis into AI_Import and Jobs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Only shortlisted jobs move into Applications after you personally approve them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Never let AI submit applications automatically at this stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Current scoring</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Technical 30% + Experience 20% + Role 15% + PPO 15% + Compensation 10% + Opportunity Quality 10%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Hard blockers</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility or availability failure forces SKIP regardless of score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Compensation</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Guaranteed/fixed pay is what counts toward the ₹25,000 minimum; incentive-only amounts are not treated as guaranteed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -662,7 +1149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -890,7 +1377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1540,13 +2027,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL544"/>
+  <dimension ref="A1:AL545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="10"/>
@@ -20741,7 +21228,6 @@
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="W505" t="inlineStr"/>
       <c r="X505" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Fullstack_Resume.pdf</t>
@@ -20800,7 +21286,6 @@
           <t>No explicit mention of PPO or conversion in the snippet.</t>
         </is>
       </c>
-      <c r="AJ505" t="inlineStr"/>
       <c r="AK505" t="inlineStr">
         <is>
           <t>Stipend amount is not disclosed (Competitive stipend)</t>
@@ -20843,7 +21328,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr"/>
       <c r="I506" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -20859,7 +21343,6 @@
           <t>Modern web technologies; Frameworks</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr"/>
       <c r="M506" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Job Description 
@@ -20897,7 +21380,6 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="W506" t="inlineStr"/>
       <c r="X506" t="inlineStr">
         <is>
           <t>Default Full Stack / Software Engineering Resume</t>
@@ -20956,7 +21438,6 @@
           <t>PPO/conversion is not explicitly mentioned in the snippet</t>
         </is>
       </c>
-      <c r="AJ506" t="inlineStr"/>
       <c r="AK506" t="inlineStr">
         <is>
           <t>Job description snippet is very brief and lacks specific details on compensation, duration, and stack</t>
@@ -20999,7 +21480,6 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr"/>
       <c r="I507" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -21010,8 +21490,6 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
-      <c r="L507" t="inlineStr"/>
       <c r="M507" t="inlineStr">
         <is>
           <t>&amp;nbsp;...world works. 
@@ -21051,7 +21529,6 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="W507" t="inlineStr"/>
       <c r="X507" t="inlineStr">
         <is>
           <t>Default Full Stack / Software Engineering Resume</t>
@@ -21110,7 +21587,6 @@
           <t>No explicit PPO or conversion mention found in the truncated JD snippet.</t>
         </is>
       </c>
-      <c r="AJ507" t="inlineStr"/>
       <c r="AK507" t="inlineStr">
         <is>
           <t>Job description snippet is heavily truncated and lacks technical details.</t>
@@ -21173,7 +21649,6 @@
           <t>Software Development; Testing</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr">
         <is>
           <t>&amp;nbsp;...streamlined, time-conscious process designed to ensure high-quality placements and complete satisfaction. 
@@ -21211,7 +21686,6 @@
           <t>STRETCH</t>
         </is>
       </c>
-      <c r="W508" t="inlineStr"/>
       <c r="X508" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Software_Engineering_Resume.pdf</t>
@@ -21270,7 +21744,6 @@
           <t>No mention of PPO or conversion in the job snippet.</t>
         </is>
       </c>
-      <c r="AJ508" t="inlineStr"/>
       <c r="AK508" t="inlineStr">
         <is>
           <t>Vague job description snippet without specific technology requirements or stipend amounts</t>
@@ -21333,7 +21806,6 @@
           <t>Go; Backend programming language</t>
         </is>
       </c>
-      <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr">
         <is>
           <t>&amp;nbsp;...technologies related to Go development. 
@@ -21436,7 +21908,6 @@
           <t>No mention of PPO or conversion in the snippet.</t>
         </is>
       </c>
-      <c r="AJ509" t="inlineStr"/>
       <c r="AK509" t="inlineStr">
         <is>
           <t>Stipend is not disclosed; Go development is mentioned</t>
@@ -21499,7 +21970,6 @@
           <t>Full Stack Development; Software Engineering</t>
         </is>
       </c>
-      <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr">
         <is>
           <t>&amp;nbsp;...We're Hiring: SDE1 and Tech &lt;b&gt;Intern &lt;/b&gt;(Paid - INR 25K to 50K)
@@ -21538,7 +22008,6 @@
           <t>APPLY</t>
         </is>
       </c>
-      <c r="W510" t="inlineStr"/>
       <c r="X510" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Full_Stack_Resume.pdf</t>
@@ -21597,7 +22066,6 @@
           <t>No explicit mention of PPO or conversion in the snippet.</t>
         </is>
       </c>
-      <c r="AJ510" t="inlineStr"/>
       <c r="AK510" t="inlineStr">
         <is>
           <t>Company name states 'Under Rebranding'</t>
@@ -21884,7 +22352,6 @@
           <t>No explicit PPO or conversion mention found in the snippet.</t>
         </is>
       </c>
-      <c r="AJ512" t="inlineStr"/>
       <c r="AK512" t="inlineStr">
         <is>
           <t>Unspecified stipend</t>
@@ -21947,7 +22414,6 @@
           <t>Python; Django; React</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr">
         <is>
           <t>&amp;nbsp;...prepare them to become future-ready creators - entrepreneurs, &lt;b&gt;engineers,&lt;/b&gt; and scientists. With a curriculum accredited by  STEM.org...&amp;nbsp;&amp;nbsp;...for coding and AI education. 
@@ -22048,7 +22514,6 @@
           <t>No mention of PPO or conversion in the job description snippet</t>
         </is>
       </c>
-      <c r="AJ513" t="inlineStr"/>
       <c r="AK513" t="inlineStr">
         <is>
           <t>Incomplete job description snippet providing limited details on stipend and duration</t>
@@ -22091,7 +22556,6 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr"/>
       <c r="I514" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -22215,7 +22679,6 @@
           <t>No explicit mention of PPO or conversion in the snippet</t>
         </is>
       </c>
-      <c r="AJ514" t="inlineStr"/>
       <c r="AK514" t="inlineStr">
         <is>
           <t>Stipend information is missing</t>
@@ -22278,7 +22741,6 @@
           <t>Agile; Modern programming languages</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr"/>
       <c r="M515" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Job description  As a &lt;b&gt;Software &lt;/b&gt;Developer &lt;b&gt;Intern,&lt;/b&gt; you will: 
@@ -22317,7 +22779,6 @@
           <t>STRETCH</t>
         </is>
       </c>
-      <c r="W515" t="inlineStr"/>
       <c r="X515" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Software_Engineer_Resume.pdf</t>
@@ -22376,7 +22837,6 @@
           <t>No mention of PPO or conversion in the job description snippet</t>
         </is>
       </c>
-      <c r="AJ515" t="inlineStr"/>
       <c r="AK515" t="inlineStr">
         <is>
           <t>Job description snippet is very vague</t>
@@ -22485,7 +22945,6 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="W516" t="inlineStr"/>
       <c r="X516" t="inlineStr">
         <is>
           <t>Amaan_Ahmed_Fullstack_Resume.pdf</t>
@@ -22544,7 +23003,6 @@
           <t>No explicit mention of PPO or conversion in the job description snippet.</t>
         </is>
       </c>
-      <c r="AJ516" t="inlineStr"/>
       <c r="AK516" t="inlineStr">
         <is>
           <t>Stipend details not provided; Vague and brief job description snippet</t>
@@ -22607,7 +23065,6 @@
           <t>NodeJS; Typescript; Git; MySQL</t>
         </is>
       </c>
-      <c r="L517" t="inlineStr"/>
       <c r="M517" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Job Description 
@@ -22709,8 +23166,6 @@
           <t>Job description does not explicitly mention PPO or conversion.</t>
         </is>
       </c>
-      <c r="AJ517" t="inlineStr"/>
-      <c r="AK517" t="inlineStr"/>
       <c r="AL517" t="inlineStr">
         <is>
           <t>Node.js architecture and event loop; TypeScript fundamentals and migration from JS; MySQL queries, indexing, and joins; Git workflows and branch management</t>
@@ -22768,7 +23223,6 @@
           <t>MERN; MongoDB; Express.js; React.js; Node.js</t>
         </is>
       </c>
-      <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr">
         <is>
           <t>&amp;nbsp;...MERN Developer – Internship + Full-Time Opportunity  Apply Link:    Apply Here 
@@ -22811,7 +23265,6 @@
           <t>APPLY ASAP</t>
         </is>
       </c>
-      <c r="W518" t="inlineStr"/>
       <c r="X518" t="inlineStr">
         <is>
           <t>Amaan_FullStack_MERN_Resume.pdf</t>
@@ -22832,7 +23285,6 @@
           <t>Eligible</t>
         </is>
       </c>
-      <c r="AB518" t="inlineStr"/>
       <c r="AC518" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -22866,7 +23318,6 @@
           <t>Internship + Full-Time Opportunity / CTC: 3.6 - 4.2 LPA</t>
         </is>
       </c>
-      <c r="AJ518" t="inlineStr"/>
       <c r="AK518" t="inlineStr">
         <is>
           <t>Stipend of Rs 20,000/month is below Amaan's minimum target of ₹25,000/month</t>
@@ -22929,7 +23380,6 @@
           <t>Communication; Management; Coding; CRM systems; Technical support; Software development; APIs; Documentation; Community engagement; Workflow</t>
         </is>
       </c>
-      <c r="L519" t="inlineStr"/>
       <c r="M519" t="inlineStr">
         <is>
           <t>&amp;nbsp;...About Us 
@@ -22992,7 +23442,6 @@
           <t>Eligible</t>
         </is>
       </c>
-      <c r="AB519" t="inlineStr"/>
       <c r="AC519" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -23026,7 +23475,6 @@
           <t>No mention of PPO or conversion in the job snippet</t>
         </is>
       </c>
-      <c r="AJ519" t="inlineStr"/>
       <c r="AK519" t="inlineStr">
         <is>
           <t>Role is Developer Relations rather than core Software Engineering or Full Stack Development</t>
@@ -23089,7 +23537,6 @@
           <t>AI; Machine Learning</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr"/>
       <c r="M520" t="inlineStr">
         <is>
           <t xml:space="preserve"> Company Description 
@@ -23191,7 +23638,6 @@
           <t>Not mentioned in the truncated job snippet</t>
         </is>
       </c>
-      <c r="AJ520" t="inlineStr"/>
       <c r="AK520" t="inlineStr">
         <is>
           <t>Truncated job description snippet; Missing stipend information</t>
@@ -23362,7 +23808,6 @@
           <t>No mention of PPO or conversion in the job snippet.</t>
         </is>
       </c>
-      <c r="AJ521" t="inlineStr"/>
       <c r="AK521" t="inlineStr">
         <is>
           <t>Role is QA Engineer, which does not align well with target roles like Full Stack, Backend, Software Engineering, DevOps, or AI.</t>
@@ -23425,7 +23870,6 @@
           <t>Full-Stack Development</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr"/>
       <c r="M522" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Position: &lt;b&gt;Full-Stack Developer &lt;/b&gt;
@@ -23466,7 +23910,6 @@
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="W522" t="inlineStr"/>
       <c r="X522" t="inlineStr">
         <is>
           <t>Amaan_Ahmed_Full_Stack_Resume.pdf</t>
@@ -23525,7 +23968,6 @@
           <t>No mention of PPO or conversion in the job snippet</t>
         </is>
       </c>
-      <c r="AJ522" t="inlineStr"/>
       <c r="AK522" t="inlineStr">
         <is>
           <t>Stipend not disclosed; PPO terms not disclosed</t>
@@ -23568,7 +24010,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr"/>
       <c r="I523" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -23584,7 +24025,6 @@
           <t>Full Stack Development; Web Development; UI/UX Implementation</t>
         </is>
       </c>
-      <c r="L523" t="inlineStr"/>
       <c r="M523" t="inlineStr">
         <is>
           <t>&amp;nbsp;...™ is an early-stage innovation project exploring AI-driven, non-addictive mental-health solutions. 
@@ -23622,7 +24062,6 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="W523" t="inlineStr"/>
       <c r="X523" t="inlineStr">
         <is>
           <t>Amaan_FullStack_Resume</t>
@@ -23681,7 +24120,6 @@
           <t>No mention of PPO or conversion.</t>
         </is>
       </c>
-      <c r="AJ523" t="inlineStr"/>
       <c r="AK523" t="inlineStr">
         <is>
           <t>Early-stage innovation project with sparse details on compensation and duration.</t>
@@ -23724,7 +24162,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr"/>
       <c r="I524" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -23740,7 +24177,6 @@
           <t>Front-end development; Full-Stack Development</t>
         </is>
       </c>
-      <c r="L524" t="inlineStr"/>
       <c r="M524" t="inlineStr">
         <is>
           <t>&amp;nbsp;...future of mobility by building a comprehensive end-to-end EV &lt;b&gt;Stack.&lt;/b&gt; From high-performance battery systems to cutting-edge...&amp;nbsp;&amp;nbsp;...sustainable and electrified transportation. 
@@ -23779,7 +24215,6 @@
           <t>STRETCH</t>
         </is>
       </c>
-      <c r="W524" t="inlineStr"/>
       <c r="X524" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Software_Engineer_Resume.pdf</t>
@@ -23838,7 +24273,6 @@
           <t>No explicit mention of PPO or conversion in the job description snippet</t>
         </is>
       </c>
-      <c r="AJ524" t="inlineStr"/>
       <c r="AK524" t="inlineStr">
         <is>
           <t>Incomplete job description snippet provided; Stipend information missing</t>
@@ -23881,7 +24315,6 @@
           <t>On-site</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr"/>
       <c r="I525" t="inlineStr">
         <is>
           <t>3 months</t>
@@ -23897,7 +24330,6 @@
           <t>Full Stack Development</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr"/>
       <c r="M525" t="inlineStr">
         <is>
           <t>&amp;nbsp;...collaborate, and grow. Our team is passionate about innovation and creating impactful digital solutions.  We are looking for a  &lt;b&gt;Full Stack Developer Intern &lt;/b&gt; to join us for a 3-month internship  at our Bengaluru office. This is a great opportunity to gain hands-on experience...&amp;nbsp;</t>
@@ -23934,7 +24366,6 @@
           <t>STRETCH</t>
         </is>
       </c>
-      <c r="W525" t="inlineStr"/>
       <c r="X525" t="inlineStr">
         <is>
           <t>Full Stack Developer Resume</t>
@@ -23993,7 +24424,6 @@
           <t>No mention of PPO or conversion in the job snippet.</t>
         </is>
       </c>
-      <c r="AJ525" t="inlineStr"/>
       <c r="AK525" t="inlineStr">
         <is>
           <t>Stipend details are not provided.</t>
@@ -24056,7 +24486,6 @@
           <t>React; PHP; Front-end Development; Back-end Development</t>
         </is>
       </c>
-      <c r="L526" t="inlineStr"/>
       <c r="M526" t="inlineStr">
         <is>
           <t>&amp;nbsp;...ensure an exceptional user experience and secure transactions. 
@@ -24120,7 +24549,6 @@
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="AB526" t="inlineStr"/>
       <c r="AC526" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -24154,7 +24582,6 @@
           <t>No mention of PPO or conversion in the job description snippet.</t>
         </is>
       </c>
-      <c r="AJ526" t="inlineStr"/>
       <c r="AK526" t="inlineStr">
         <is>
           <t>Non-paid internship; Requires PHP which is not in candidate primary demonstrated stack</t>
@@ -24217,7 +24644,6 @@
           <t>Full Stack Web Development</t>
         </is>
       </c>
-      <c r="L527" t="inlineStr"/>
       <c r="M527" t="inlineStr">
         <is>
           <t>&amp;nbsp;...application development, and digital marketing. AI4SEES also &lt;b&gt;develops &lt;/b&gt;SaaS and PaaS products, IoT and cloud technology...&amp;nbsp;&amp;nbsp;...and clients. 
@@ -24255,7 +24681,6 @@
           <t>STRETCH</t>
         </is>
       </c>
-      <c r="W527" t="inlineStr"/>
       <c r="X527" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Fullstack_Resume.pdf</t>
@@ -24314,7 +24739,6 @@
           <t>No mention of PPO or conversion in the job description snippet.</t>
         </is>
       </c>
-      <c r="AJ527" t="inlineStr"/>
       <c r="AK527" t="inlineStr">
         <is>
           <t>Incomplete job description snippet with missing stipend and duration details</t>
@@ -24377,7 +24801,6 @@
           <t>GIS; Geospatial Data; Mapping; Remote Sensing</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr"/>
       <c r="M528" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Location: Bangalore 
@@ -24481,7 +24904,6 @@
           <t>No mention of conversion to full-time employment or PPO in the job snippet.</t>
         </is>
       </c>
-      <c r="AJ528" t="inlineStr"/>
       <c r="AK528" t="inlineStr">
         <is>
           <t>Role is heavily focused on GIS and Remote Sensing which is outside Amaan's core software engineering skill set.</t>
@@ -24544,7 +24966,6 @@
           <t>Full Stack Development</t>
         </is>
       </c>
-      <c r="L529" t="inlineStr"/>
       <c r="M529" t="inlineStr">
         <is>
           <t>&amp;nbsp;...&lt;b&gt;Full Stack Developer Intern &lt;/b&gt; Company:  Impacto Digifin Technologies Pvt. Ltd. 
@@ -24587,7 +25008,6 @@
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="W529" t="inlineStr"/>
       <c r="X529" t="inlineStr">
         <is>
           <t>Default Full Stack Resume</t>
@@ -24713,7 +25133,6 @@
           <t>Accounts; Compliance; Audits</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Location: Bangalore 
@@ -24768,7 +25187,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="Z530" t="inlineStr"/>
       <c r="AA530" t="inlineStr">
         <is>
           <t>NOT ELIGIBLE</t>
@@ -24822,7 +25240,6 @@
           <t>Mismatch in domain (Finance/Compliance vs Computer Applications/Software Engineering)</t>
         </is>
       </c>
-      <c r="AL530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="B531" t="inlineStr">
@@ -24980,7 +25397,6 @@
           <t>No explicit PPO or conversion mention found in the job description snippet.</t>
         </is>
       </c>
-      <c r="AJ531" t="inlineStr"/>
       <c r="AK531" t="inlineStr">
         <is>
           <t>Stipend information missing; PPO information missing</t>
@@ -25043,7 +25459,6 @@
           <t>Flutter; Mobile App Development</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr"/>
       <c r="M532" t="inlineStr">
         <is>
           <t>Job Description: Flutter &lt;b&gt;SDE Intern &lt;/b&gt;(Mobile App Development)
@@ -25101,7 +25516,6 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="Z532" t="inlineStr"/>
       <c r="AA532" t="inlineStr">
         <is>
           <t>Eligible</t>
@@ -25192,7 +25606,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr"/>
       <c r="I533" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -25252,7 +25665,6 @@
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="W533" t="inlineStr"/>
       <c r="X533" t="inlineStr">
         <is>
           <t>Default Full Stack / Backend Resume</t>
@@ -25311,8 +25723,6 @@
           <t>No explicit mention of PPO or conversion in the job snippet.</t>
         </is>
       </c>
-      <c r="AJ533" t="inlineStr"/>
-      <c r="AK533" t="inlineStr"/>
       <c r="AL533" t="inlineStr">
         <is>
           <t>Backend fundamentals in Node.js or Python; Project architecture and independent problem-solving; API design and system scaling</t>
@@ -25479,7 +25889,6 @@
           <t>No explicit mention of PPO or conversion in the snippet</t>
         </is>
       </c>
-      <c r="AJ534" t="inlineStr"/>
       <c r="AK534" t="inlineStr">
         <is>
           <t>Role is QA Automation, which diverges from target development and engineering roles</t>
@@ -25651,7 +26060,6 @@
           <t>No mention of PPO or conversion in the job description snippet.</t>
         </is>
       </c>
-      <c r="AJ535" t="inlineStr"/>
       <c r="AK535" t="inlineStr">
         <is>
           <t>Role is Data Analyst, whereas target roles are Software Engineering/Backend/Full Stack.</t>
@@ -25781,7 +26189,6 @@
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="AB536" t="inlineStr"/>
       <c r="AC536" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -25815,7 +26222,6 @@
           <t>No mention of PPO or conversion in the job description.</t>
         </is>
       </c>
-      <c r="AJ536" t="inlineStr"/>
       <c r="AK536" t="inlineStr">
         <is>
           <t>Minimum stipend falls slightly below the Rs 25,000/month target at the lower end (approx Rs 20,833/month).</t>
@@ -25983,8 +26389,6 @@
           <t>Intern for 6 months and then will be converted into full-time role</t>
         </is>
       </c>
-      <c r="AJ537" t="inlineStr"/>
-      <c r="AK537" t="inlineStr"/>
       <c r="AL537" t="inlineStr">
         <is>
           <t>Python and Node.js development experience; SQL and database management; Past projects like StaySphere or Zenvest; Readiness for conversion to full-time role after 6 months</t>
@@ -26085,7 +26489,6 @@
           <t>STRETCH</t>
         </is>
       </c>
-      <c r="W538" t="inlineStr"/>
       <c r="X538" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Software_Engineer_Resume.pdf</t>
@@ -26144,7 +26547,6 @@
           <t>No explicit PPO or conversion mention found in snippet</t>
         </is>
       </c>
-      <c r="AJ538" t="inlineStr"/>
       <c r="AK538" t="inlineStr">
         <is>
           <t>Vague job description snippet with missing stipend and duration details</t>
@@ -26202,8 +26604,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
-      <c r="L539" t="inlineStr"/>
       <c r="M539" t="inlineStr">
         <is>
           <t>&amp;nbsp;...ABOUT THE JOB 
@@ -26241,7 +26641,6 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="W539" t="inlineStr"/>
       <c r="X539" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Software_Engineer_Resume.pdf</t>
@@ -26300,7 +26699,6 @@
           <t>No explicit mention of PPO or conversion in the snippet.</t>
         </is>
       </c>
-      <c r="AJ539" t="inlineStr"/>
       <c r="AK539" t="inlineStr">
         <is>
           <t>Location mismatch (Job is in Pune, candidate target location not explicitly restricted but relevant consideration)</t>
@@ -26363,7 +26761,6 @@
           <t>Rapid Prototyping; Chatbots; Workflow Automations</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr"/>
       <c r="M540" t="inlineStr">
         <is>
           <t>&amp;nbsp;...ideas. 
@@ -26467,7 +26864,6 @@
           <t>No mention of PPO or conversion in the job description.</t>
         </is>
       </c>
-      <c r="AJ540" t="inlineStr"/>
       <c r="AK540" t="inlineStr">
         <is>
           <t>Stipend is below the minimum target of ₹25,000/month; No mention of PPO</t>
@@ -26530,7 +26926,6 @@
           <t>AI-powered applications; Prototypes development; Performance metrics</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr"/>
       <c r="M541" t="inlineStr">
         <is>
           <t>&amp;nbsp;...AI Engineer &lt;b&gt;Intern &lt;/b&gt; Location: Bangalore 
@@ -26636,7 +27031,6 @@
           <t>No mention of PPO or conversion to full-time role in the snippet</t>
         </is>
       </c>
-      <c r="AJ541" t="inlineStr"/>
       <c r="AK541" t="inlineStr">
         <is>
           <t>Stipend amount is unknown despite being marked as paid</t>
@@ -26679,7 +27073,6 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr"/>
       <c r="I542" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -26695,7 +27088,6 @@
           <t>Node.js; Python; HTML; CSS; JavaScript; React</t>
         </is>
       </c>
-      <c r="L542" t="inlineStr"/>
       <c r="M542" t="inlineStr">
         <is>
           <t>&amp;nbsp;...experience in software development and technology operations. As a Tech &lt;b&gt;Intern,&lt;/b&gt; you will work closely with our engineering team on live projects...&amp;nbsp;&amp;nbsp;...Basics: Familiarity with at least one backend language (e.g., &lt;b&gt;Node.js,&lt;/b&gt; Python) and frontend basics (HTML/CSS/JavaScript or React)....&amp;nbsp;</t>
@@ -26732,7 +27124,6 @@
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="W542" t="inlineStr"/>
       <c r="X542" t="inlineStr">
         <is>
           <t>Full Stack / Software Engineering Resume</t>
@@ -26753,7 +27144,6 @@
           <t>Eligible</t>
         </is>
       </c>
-      <c r="AB542" t="inlineStr"/>
       <c r="AC542" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -26787,7 +27177,6 @@
           <t>No mention of PPO or conversion in the job snippet.</t>
         </is>
       </c>
-      <c r="AJ542" t="inlineStr"/>
       <c r="AK542" t="inlineStr">
         <is>
           <t>Stipend is not disclosed.</t>
@@ -26855,7 +27244,6 @@
           <t>Software Development</t>
         </is>
       </c>
-      <c r="L543" t="inlineStr"/>
       <c r="M543" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Internship Opportunity | &lt;b&gt;Software &lt;/b&gt;Development &lt;b&gt;Engineering &lt;/b&gt;| PPO opportunity 
@@ -26897,7 +27285,6 @@
           <t>APPLY ASAP</t>
         </is>
       </c>
-      <c r="W543" t="inlineStr"/>
       <c r="X543" t="inlineStr">
         <is>
           <t>Amaanuddin_Ahmed_Fullstack_Resume.pdf</t>
@@ -26956,8 +27343,6 @@
           <t>PPO opportunity mentioned in the job snippet.</t>
         </is>
       </c>
-      <c r="AJ543" t="inlineStr"/>
-      <c r="AK543" t="inlineStr"/>
       <c r="AL543" t="inlineStr">
         <is>
           <t>Full stack development fundamentals; Problem solving and coding; Project architecture and deployment</t>
@@ -27020,7 +27405,6 @@
           <t>Django; ReactJS; Third-party APIs</t>
         </is>
       </c>
-      <c r="L544" t="inlineStr"/>
       <c r="M544" t="inlineStr">
         <is>
           <t>&amp;nbsp;...them increase their sales on Amazon. We are looking for a tech &lt;b&gt;intern &lt;/b&gt;to help us develop our product. 
@@ -27124,7 +27508,6 @@
           <t>No mention of PPO or conversion in the job snippet</t>
         </is>
       </c>
-      <c r="AJ544" t="inlineStr"/>
       <c r="AK544" t="inlineStr">
         <is>
           <t>Very limited job description snippet provided; Stipend details not disclosed</t>
@@ -27133,6 +27516,175 @@
       <c r="AL544" t="inlineStr">
         <is>
           <t>Django framework fundamentals; React.js state management; REST API integration; SDLC practices</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>JOVEO-260909-1</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Joveo</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern / Back End Developer</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>https://in.jooble.org/jdp/5995199810772247499</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>AI Analyzer</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>On-site (5 days a week)</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>NOT_MENTIONED</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Node.js; Express.js; React.js; Next.js</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Title  : Software Engineering &lt;b&gt;Intern &lt;/b&gt;
+ Location  : Bengaluru, India ( 5 days a week)
+ Timings  : 2-9 pm  About Joveo  As the global...&amp;nbsp;&amp;nbsp;...products from whiteboard to working prototype. 
+ Ship across the &lt;b&gt;full stack,&lt;/b&gt; React and Next.js on the front, Node.js and Express on the back...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="N545" t="n">
+        <v>66</v>
+      </c>
+      <c r="O545" t="n">
+        <v>25</v>
+      </c>
+      <c r="P545" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>15</v>
+      </c>
+      <c r="R545" t="n">
+        <v>0</v>
+      </c>
+      <c r="S545" t="n">
+        <v>0</v>
+      </c>
+      <c r="T545" t="n">
+        <v>6</v>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>STRETCH</t>
+        </is>
+      </c>
+      <c r="V545" t="inlineStr">
+        <is>
+          <t>STRETCH</t>
+        </is>
+      </c>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>Default Full Stack / MERN Resume</t>
+        </is>
+      </c>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z545" t="inlineStr">
+        <is>
+          <t>Matches primary MERN stack skill set (Node.js, Express.js, React.js); Good opportunity for full stack experience</t>
+        </is>
+      </c>
+      <c r="AA545" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="AB545" t="inlineStr">
+        <is>
+          <t>Candidate is pursuing MCA; Skills match the technical expectations of the role</t>
+        </is>
+      </c>
+      <c r="AC545" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AD545" t="inlineStr">
+        <is>
+          <t>Availability not explicitly stated in the job description or career brain.</t>
+        </is>
+      </c>
+      <c r="AE545" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AF545" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG545" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH545" t="inlineStr">
+        <is>
+          <t>NOT_MENTIONED</t>
+        </is>
+      </c>
+      <c r="AI545" t="inlineStr">
+        <is>
+          <t>No mention of PPO or conversion in the job snippet.</t>
+        </is>
+      </c>
+      <c r="AK545" t="inlineStr">
+        <is>
+          <t>Stipend is not disclosed; Fixed shift timing (2-9 pm) might be required</t>
+        </is>
+      </c>
+      <c r="AL545" t="inlineStr">
+        <is>
+          <t>Node.js and Express.js architecture; React.js and Next.js differences/usage; Full stack system design and prototyping</t>
         </is>
       </c>
     </row>
@@ -27165,7 +27717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38275,7 +38827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48358,7 +48910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48390,10 +48942,8 @@
           <t>Metric</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>544</v>
       </c>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
@@ -48410,9 +48960,8 @@
           <t>Total Jobs</t>
         </is>
       </c>
-      <c r="B3" s="2">
-        <f>COUNTA(Jobs!A2:A500)</f>
-        <v/>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="3" t="inlineStr">
@@ -48441,9 +48990,8 @@
           <t>Shortlisted / Apply-level Jobs</t>
         </is>
       </c>
-      <c r="B4" s="2">
-        <f>COUNTIF(Jobs!V2:V500,"APPLY")+COUNTIF(Jobs!V2:V500,"APPLY ASAP")</f>
-        <v/>
+      <c r="B4" s="2" t="n">
+        <v>499</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
@@ -48501,9 +49049,8 @@
           <t>OAs</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>COUNTIF(Applications!H2:H500,"OA")</f>
-        <v/>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
@@ -48531,9 +49078,8 @@
           <t>Interviews</t>
         </is>
       </c>
-      <c r="B7" s="2">
-        <f>COUNTIF(Applications!H2:H500,"Technical Interview")+COUNTIF(Applications!H2:H500,"HR/Manager")</f>
-        <v/>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
@@ -48753,7 +49299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -55246,126 +55792,4 @@
   <autoFilter ref="A1:AK499"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="105" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="39" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>AI → CRM workflow</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Run a JD through the AI Job Analyzer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Copy the structured JSON result into the importer script/tool we will build next.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>The importer maps the analysis into AI_Import and Jobs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Only shortlisted jobs move into Applications after you personally approve them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Never let AI submit applications automatically at this stage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Current scoring</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Technical 30% + Experience 20% + Role 15% + PPO 15% + Compensation 10% + Opportunity Quality 10%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Hard blockers</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility or availability failure forces SKIP regardless of score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Compensation</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Guaranteed/fixed pay is what counts toward the ₹25,000 minimum; incentive-only amounts are not treated as guaranteed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>